--- a/mosip_master/xlsx/reg_center_type.xlsx
+++ b/mosip_master/xlsx/reg_center_type.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kames\IdeaProjects\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SLUDI Offline Training\mosip-data-1.3.0\mosip-data-1.3.0\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A8DE9C3-E1C6-4A63-B311-6B5E2B07DD7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AE53DDC-B370-47B4-B8B4-CAA3234A812E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
   <si>
     <t>lang_code</t>
   </si>
@@ -57,42 +57,6 @@
     <t>TRUE</t>
   </si>
   <si>
-    <t>fra</t>
-  </si>
-  <si>
-    <t>Ordinaire</t>
-  </si>
-  <si>
-    <t>Centre dinscription régulière</t>
-  </si>
-  <si>
-    <t>ara</t>
-  </si>
-  <si>
-    <t>عادي</t>
-  </si>
-  <si>
-    <t>مركز التسجيل العادي</t>
-  </si>
-  <si>
-    <t>kan</t>
-  </si>
-  <si>
-    <t>ನಿಯಮಿತ</t>
-  </si>
-  <si>
-    <t>ನಿಯಮಿತ ನೋಂದಣಿ ಕೇಂದ್ರ</t>
-  </si>
-  <si>
-    <t>hin</t>
-  </si>
-  <si>
-    <t>नियमित</t>
-  </si>
-  <si>
-    <t>नियमित पंजीकरण केंद्र</t>
-  </si>
-  <si>
     <t>tam</t>
   </si>
   <si>
@@ -102,10 +66,13 @@
     <t>வழக்கமான பதிவு மையம்</t>
   </si>
   <si>
-    <t>spa</t>
-  </si>
-  <si>
-    <t>Centro de registro regular</t>
+    <t>sin</t>
+  </si>
+  <si>
+    <t>සාමාන්‍ය</t>
+  </si>
+  <si>
+    <t>සාමාන්‍ය ලියාපදිංචි කිරීමේ මධ්‍යස්ථානය</t>
   </si>
 </sst>
 </file>
@@ -162,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -170,12 +137,6 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -491,15 +452,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultColWidth="8.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="21.90625" customWidth="1"/>
-    <col min="4" max="4" width="34.08984375" customWidth="1"/>
-    <col min="5" max="5" width="8.453125" style="1"/>
+    <col min="3" max="3" width="21.88671875" customWidth="1"/>
+    <col min="4" max="4" width="34.109375" customWidth="1"/>
+    <col min="5" max="5" width="8.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -516,7 +477,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -533,7 +494,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -550,93 +511,25 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="1" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>